--- a/output/pdf_financials_xlsx/FRG.xlsx
+++ b/output/pdf_financials_xlsx/FRG.xlsx
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.418074</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.793528</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>7.931408</v>
       </c>
     </row>
     <row r="93">
@@ -3296,7 +3296,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -3750,7 +3754,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>2.418074</v>
       </c>

--- a/output/pdf_financials_xlsx/FRG.xlsx
+++ b/output/pdf_financials_xlsx/FRG.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.034546</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.344036</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.380068</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.034546</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.344036</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.380068</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.048142</v>
+        <v>0.013596</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.6632209999999999</v>
+        <v>0.319185</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.795925</v>
+        <v>0.415857</v>
       </c>
     </row>
     <row r="49">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">

--- a/output/pdf_financials_xlsx/FRG.xlsx
+++ b/output/pdf_financials_xlsx/FRG.xlsx
@@ -751,8 +751,10 @@
       <c r="B20" s="3" t="n">
         <v>-7.997969</v>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>-3.125532</v>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D20" s="3" t="n">
         <v>-6.303874</v>
@@ -768,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>0.003709</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -5715,7 +5717,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E98" s="5" t="n">
         <v>0.402</v>
       </c>
@@ -6887,7 +6893,11 @@
           <t>Income from discontinued operations</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
